--- a/data/référentiels/IFP_réferentiels_2026.xlsx
+++ b/data/référentiels/IFP_réferentiels_2026.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data For Good\IFP Oxfam Projet Integration\14_IndexFeminisationPouvoir\data\référentiels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68100335-F380-499D-A99E-87C1A126EBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95611D49-ED83-4560-821D-407954A7266D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="1" xr2:uid="{FAE432B0-83A5-4652-A7ED-A9D22361CDED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="1" xr2:uid="{FAE432B0-83A5-4652-A7ED-A9D22361CDED}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="5" r:id="rId1"/>
     <sheet name="ref_figures" sheetId="7" r:id="rId2"/>
-    <sheet name="ref_agences_hautes_autorités" sheetId="3" r:id="rId3"/>
+    <sheet name="ref_agences_hautes_autorites" sheetId="3" r:id="rId3"/>
     <sheet name="ref_hautes_juridictions" sheetId="4" r:id="rId4"/>
-    <sheet name="ref_postes_régaliens" sheetId="6" r:id="rId5"/>
+    <sheet name="ref_postes_regaliens" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ref_agences_hautes_autorités" localSheetId="2">ref_agences_hautes_autorités!$A$1:$B$39</definedName>
+    <definedName name="ref_agences_hautes_autorités" localSheetId="2">ref_agences_hautes_autorites!$A$1:$B$39</definedName>
     <definedName name="ref_hautes_juridictions" localSheetId="3">ref_hautes_juridictions!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="200">
   <si>
     <t>administration</t>
   </si>
@@ -456,30 +456,15 @@
     <t>gouvernement</t>
   </si>
   <si>
-    <t>préfectures</t>
-  </si>
-  <si>
-    <t>gouv_postes_régaliens</t>
-  </si>
-  <si>
-    <t>cabinet_président</t>
-  </si>
-  <si>
     <t>cabinet_premier_ministre</t>
   </si>
   <si>
-    <t>dir_cab_ministères</t>
-  </si>
-  <si>
     <t>hautes_juridictions</t>
   </si>
   <si>
     <t>ambassades</t>
   </si>
   <si>
-    <t>agences_hautes_autorités</t>
-  </si>
-  <si>
     <t>figure1a</t>
   </si>
   <si>
@@ -606,19 +591,64 @@
     <t>haute_autorite</t>
   </si>
   <si>
-    <t>json_tag_level_1</t>
-  </si>
-  <si>
-    <t>json_tag_level_2</t>
-  </si>
-  <si>
-    <t>json_tag_level_0</t>
-  </si>
-  <si>
     <t>pouvoir</t>
   </si>
   <si>
     <t>pouvoir_autres</t>
+  </si>
+  <si>
+    <t>mairies</t>
+  </si>
+  <si>
+    <t>mairies_prefectures</t>
+  </si>
+  <si>
+    <t>Pourcentage de femmes maires d'arrondissements PLM</t>
+  </si>
+  <si>
+    <t>partis_politiques</t>
+  </si>
+  <si>
+    <t>mairies_plm_arr</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>maires</t>
+  </si>
+  <si>
+    <t>mairesPrefecture</t>
+  </si>
+  <si>
+    <t>mairesPLMArrondissement</t>
+  </si>
+  <si>
+    <t>parti_politique</t>
+  </si>
+  <si>
+    <t>autre</t>
+  </si>
+  <si>
+    <t>gouv_postes_regaliens</t>
+  </si>
+  <si>
+    <t>cabinet_president</t>
+  </si>
+  <si>
+    <t>dir_cab_ministeres</t>
+  </si>
+  <si>
+    <t>agences_hautes_autorites</t>
+  </si>
+  <si>
+    <t>pouvoir_type_libelle</t>
+  </si>
+  <si>
+    <t>pouvoir_categorie</t>
+  </si>
+  <si>
+    <t>pouvoir_composante</t>
   </si>
 </sst>
 </file>
@@ -772,7 +802,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -973,6 +1003,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1153,12 +1195,14 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="10" xfId="42" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1573,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A481C269-FB6B-4C4E-88AB-D572F86B4F1C}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="5" width="21.33203125" customWidth="1"/>
@@ -1582,7 +1626,7 @@
     <col min="9" max="9" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1590,31 +1634,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D1" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="E1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F1" t="s">
         <v>133</v>
       </c>
       <c r="G1" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="H1" t="s">
         <v>132</v>
       </c>
       <c r="I1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1622,10 +1663,10 @@
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
@@ -1637,30 +1678,27 @@
         <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s">
         <v>134</v>
       </c>
-      <c r="J2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>116</v>
@@ -1669,30 +1707,27 @@
         <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I3" t="s">
         <v>134</v>
       </c>
-      <c r="J3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>101</v>
@@ -1701,30 +1736,27 @@
         <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I4" t="s">
         <v>134</v>
       </c>
-      <c r="J4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>102</v>
@@ -1733,30 +1765,27 @@
         <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I5" t="s">
         <v>134</v>
       </c>
-      <c r="J5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>103</v>
@@ -1765,16 +1794,13 @@
         <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I6" t="s">
         <v>134</v>
       </c>
-      <c r="J6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1785,13 +1811,13 @@
         <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -1802,13 +1828,13 @@
         <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1819,13 +1845,13 @@
         <v>104</v>
       </c>
       <c r="H9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1836,13 +1862,13 @@
         <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -1853,13 +1879,13 @@
         <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -1870,13 +1896,13 @@
         <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -1887,13 +1913,13 @@
         <v>104</v>
       </c>
       <c r="H13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -1904,13 +1930,13 @@
         <v>104</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -1921,16 +1947,25 @@
         <v>104</v>
       </c>
       <c r="H15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
+      <c r="B16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" t="s">
+        <v>188</v>
+      </c>
       <c r="F16" s="3" t="s">
         <v>119</v>
       </c>
@@ -1938,16 +1973,25 @@
         <v>112</v>
       </c>
       <c r="H16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>89</v>
       </c>
+      <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" t="s">
+        <v>189</v>
+      </c>
       <c r="F17" s="3" t="s">
         <v>120</v>
       </c>
@@ -1955,204 +1999,256 @@
         <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I17" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>121</v>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="G18" t="s">
         <v>112</v>
       </c>
+      <c r="I18" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
         <v>112</v>
       </c>
-      <c r="H19" t="s">
-        <v>163</v>
-      </c>
+      <c r="H19" s="5"/>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G20" t="s">
         <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
         <v>112</v>
       </c>
       <c r="H21" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" t="s">
         <v>165</v>
-      </c>
-      <c r="I21" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G22" t="s">
         <v>112</v>
       </c>
       <c r="H22" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" t="s">
         <v>166</v>
-      </c>
-      <c r="I22" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="G23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>192</v>
+      </c>
+      <c r="E24" t="s">
+        <v>136</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
         <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>192</v>
+      </c>
+      <c r="E25" t="s">
+        <v>178</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" t="s">
         <v>113</v>
       </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I25" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>184</v>
+        <v>192</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G26" t="s">
         <v>113</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I26" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="B27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E27" t="s">
+        <v>179</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
         <v>113</v>
+      </c>
+      <c r="H27" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
